--- a/Data_clean/MCAS/Estados_US/Edos_USA_2015/HAWAII_2015.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2015/HAWAII_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C5">
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -485,7 +510,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C9">
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -586,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -768,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C29">
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -820,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C33">
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -859,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -890,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>San Miguel de Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C38">
@@ -903,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C39">
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>León</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -968,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C44">
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1014,7 +1194,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C47">
@@ -1025,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C48">
@@ -1038,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1069,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Ajacuba</t>
@@ -1082,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Santiago de Anaya</t>
+          <t>Santiago De Anaya</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C54">
@@ -1121,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Cabo Corrientes</t>
@@ -1191,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>El Limón</t>
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Hostotipaquillo</t>
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1269,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C66">
@@ -1282,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C67">
@@ -1295,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1308,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C69">
@@ -1321,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Talpa de Allende</t>
+          <t>Talpa De Allende</t>
         </is>
       </c>
       <c r="C70">
@@ -1334,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1347,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C72">
@@ -1360,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1373,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -1386,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1399,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Villa Corona</t>
@@ -1412,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zapotlán del Rey</t>
+          <t>Zapotlán Del Rey</t>
         </is>
       </c>
       <c r="C77">
@@ -1425,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1438,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1469,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -1482,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Huaniqueo</t>
@@ -1495,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Marcos Castellanos</t>
@@ -1508,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Nahuatzen</t>
@@ -1521,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -1534,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1547,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1560,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1573,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1586,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1617,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1648,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C94">
@@ -1661,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -1674,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -1687,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -1700,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1713,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1726,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1739,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1748,7 +2173,7 @@
         <v>19</v>
       </c>
       <c r="D101">
-        <v>0.09595959595959595</v>
+        <v>0.09595959595959597</v>
       </c>
     </row>
     <row r="102">
@@ -1759,7 +2184,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C102">
@@ -1770,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C103">
@@ -1783,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C104">
@@ -1796,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -1809,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>San Juan Atepec</t>
@@ -1822,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -1835,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>San Pedro Teutila</t>
@@ -1848,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Santa María Yucuhiti</t>
@@ -1861,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -1874,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1887,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Teotitlán de Flores Magón</t>
+          <t>Teotitlán De Flores Magón</t>
         </is>
       </c>
       <c r="C112">
@@ -1900,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C113">
@@ -1913,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1944,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -1957,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -1970,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -1983,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -1996,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C120">
@@ -2009,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -2022,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C122">
@@ -2035,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -2048,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Soltepec</t>
@@ -2061,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -2074,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -2087,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2107,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C128">
@@ -2118,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Colón</t>
@@ -2131,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2151,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C131">
@@ -2162,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -2175,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2206,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2237,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Imuris</t>
@@ -2250,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2281,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C140">
@@ -2294,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C141">
@@ -2307,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -2320,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2333,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2346,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2377,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2400,41 +3015,6 @@
       </c>
       <c r="D148">
         <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
